--- a/data/odds/EBC League 2026 Betting Odds.xlsx
+++ b/data/odds/EBC League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="49">
   <si>
     <t>Record</t>
   </si>
@@ -30,124 +30,139 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Inter Miami CF</t>
+  </si>
+  <si>
+    <t>OBJYN</t>
+  </si>
+  <si>
+    <t>Wise Warlocks</t>
+  </si>
+  <si>
+    <t>Abyss Diamond Eyes</t>
+  </si>
+  <si>
     <t>P90 Asiimov</t>
   </si>
   <si>
-    <t>Inter Miami CF</t>
-  </si>
-  <si>
-    <t>OBJYN</t>
-  </si>
-  <si>
-    <t>Abyss Diamond Eyes</t>
-  </si>
-  <si>
-    <t>Wise Warlocks</t>
-  </si>
-  <si>
     <t xml:space="preserve">First down syndrome </t>
   </si>
   <si>
+    <t>Jimoke Jukes</t>
+  </si>
+  <si>
     <t>Pleasant Valley Panthers</t>
   </si>
   <si>
-    <t>Jimoke Jukes</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-2</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>86.9%</t>
-  </si>
-  <si>
-    <t>83.7%</t>
-  </si>
-  <si>
-    <t>19.7%</t>
-  </si>
-  <si>
-    <t>9.7%</t>
-  </si>
-  <si>
-    <t>-∞</t>
-  </si>
-  <si>
-    <t>-663</t>
-  </si>
-  <si>
-    <t>-513</t>
-  </si>
-  <si>
-    <t>+408</t>
-  </si>
-  <si>
-    <t>+931</t>
+    <t>96.9%</t>
+  </si>
+  <si>
+    <t>95.9%</t>
+  </si>
+  <si>
+    <t>95.8%</t>
+  </si>
+  <si>
+    <t>74.6%</t>
+  </si>
+  <si>
+    <t>20.7%</t>
+  </si>
+  <si>
+    <t>16.1%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-3126</t>
+  </si>
+  <si>
+    <t>-2339</t>
+  </si>
+  <si>
+    <t>-2281</t>
+  </si>
+  <si>
+    <t>-294</t>
+  </si>
+  <si>
+    <t>+383</t>
+  </si>
+  <si>
+    <t>+521</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>79.1%</t>
-  </si>
-  <si>
-    <t>15.8%</t>
-  </si>
-  <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
+    <t>63.9%</t>
+  </si>
+  <si>
+    <t>36.1%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-378</t>
-  </si>
-  <si>
-    <t>+533</t>
-  </si>
-  <si>
-    <t>+2930</t>
-  </si>
-  <si>
-    <t>+5456</t>
-  </si>
-  <si>
-    <t>+∞</t>
-  </si>
-  <si>
-    <t>51.1%</t>
-  </si>
-  <si>
-    <t>43.2%</t>
-  </si>
-  <si>
-    <t>3.8%</t>
-  </si>
-  <si>
-    <t>1.9%</t>
-  </si>
-  <si>
-    <t>-104</t>
-  </si>
-  <si>
-    <t>+131</t>
-  </si>
-  <si>
-    <t>+2532</t>
-  </si>
-  <si>
-    <t>+5163</t>
+    <t>-177</t>
+  </si>
+  <si>
+    <t>+177</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>53.0%</t>
+  </si>
+  <si>
+    <t>38.4%</t>
+  </si>
+  <si>
+    <t>6.7%</t>
+  </si>
+  <si>
+    <t>0.9%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>-113</t>
+  </si>
+  <si>
+    <t>+160</t>
+  </si>
+  <si>
+    <t>+1393</t>
+  </si>
+  <si>
+    <t>+11011</t>
+  </si>
+  <si>
+    <t>+12400</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -530,10 +545,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -541,13 +556,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -558,10 +573,10 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -569,13 +584,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -583,13 +598,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -597,13 +612,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -614,10 +629,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -625,13 +640,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -652,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -660,100 +675,100 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -761,13 +776,13 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -788,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -799,13 +814,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -816,94 +831,94 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/EBC League 2026 Betting Odds.xlsx
+++ b/data/odds/EBC League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="55">
   <si>
     <t>Record</t>
   </si>
@@ -30,139 +30,157 @@
     <t>Team</t>
   </si>
   <si>
+    <t>OBJYN</t>
+  </si>
+  <si>
+    <t>Abyss Diamond Eyes</t>
+  </si>
+  <si>
     <t>Inter Miami CF</t>
   </si>
   <si>
-    <t>OBJYN</t>
+    <t>P90 Asiimov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First down syndrome </t>
+  </si>
+  <si>
+    <t>Jimoke Jukes</t>
   </si>
   <si>
     <t>Wise Warlocks</t>
   </si>
   <si>
-    <t>Abyss Diamond Eyes</t>
-  </si>
-  <si>
-    <t>P90 Asiimov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First down syndrome </t>
-  </si>
-  <si>
-    <t>Jimoke Jukes</t>
-  </si>
-  <si>
     <t>Pleasant Valley Panthers</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>96.9%</t>
-  </si>
-  <si>
-    <t>95.9%</t>
-  </si>
-  <si>
-    <t>95.8%</t>
-  </si>
-  <si>
-    <t>74.6%</t>
-  </si>
-  <si>
-    <t>20.7%</t>
-  </si>
-  <si>
-    <t>16.1%</t>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>99.6%</t>
+  </si>
+  <si>
+    <t>92.8%</t>
+  </si>
+  <si>
+    <t>82.5%</t>
+  </si>
+  <si>
+    <t>69.9%</t>
+  </si>
+  <si>
+    <t>41.9%</t>
+  </si>
+  <si>
+    <t>13.5%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-3126</t>
-  </si>
-  <si>
-    <t>-2339</t>
-  </si>
-  <si>
-    <t>-2281</t>
-  </si>
-  <si>
-    <t>-294</t>
-  </si>
-  <si>
-    <t>+383</t>
-  </si>
-  <si>
-    <t>+521</t>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-24900</t>
+  </si>
+  <si>
+    <t>-1289</t>
+  </si>
+  <si>
+    <t>-471</t>
+  </si>
+  <si>
+    <t>-232</t>
+  </si>
+  <si>
+    <t>+139</t>
+  </si>
+  <si>
+    <t>+641</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>63.9%</t>
-  </si>
-  <si>
-    <t>36.1%</t>
+    <t>82.3%</t>
+  </si>
+  <si>
+    <t>11.2%</t>
+  </si>
+  <si>
+    <t>6.0%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-177</t>
-  </si>
-  <si>
-    <t>+177</t>
+    <t>-465</t>
+  </si>
+  <si>
+    <t>+793</t>
+  </si>
+  <si>
+    <t>+1567</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>53.0%</t>
-  </si>
-  <si>
-    <t>38.4%</t>
-  </si>
-  <si>
-    <t>6.7%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
-  </si>
-  <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>-113</t>
-  </si>
-  <si>
-    <t>+160</t>
-  </si>
-  <si>
-    <t>+1393</t>
-  </si>
-  <si>
-    <t>+11011</t>
-  </si>
-  <si>
-    <t>+12400</t>
-  </si>
-  <si>
-    <t>+49900</t>
+    <t>65.1%</t>
+  </si>
+  <si>
+    <t>20.8%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>3.6%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
+  </si>
+  <si>
+    <t>-187</t>
+  </si>
+  <si>
+    <t>+381</t>
+  </si>
+  <si>
+    <t>+999</t>
+  </si>
+  <si>
+    <t>+2678</t>
+  </si>
+  <si>
+    <t>+7043</t>
   </si>
 </sst>
 </file>
@@ -545,10 +563,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -556,13 +574,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -570,13 +588,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -584,13 +602,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -598,13 +616,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -612,13 +630,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -626,13 +644,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -640,13 +658,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -667,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -681,10 +699,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -692,69 +710,69 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -762,13 +780,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -776,13 +794,13 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -803,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -814,13 +832,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -828,13 +846,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -842,41 +860,41 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -884,13 +902,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -901,10 +919,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -912,13 +930,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/EBC League 2026 Betting Odds.xlsx
+++ b/data/odds/EBC League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="52">
   <si>
     <t>Record</t>
   </si>
@@ -30,19 +30,22 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Inter Miami CF</t>
+  </si>
+  <si>
     <t>OBJYN</t>
   </si>
   <si>
     <t>Abyss Diamond Eyes</t>
   </si>
   <si>
-    <t>Inter Miami CF</t>
+    <t xml:space="preserve">First down syndrome </t>
   </si>
   <si>
     <t>P90 Asiimov</t>
   </si>
   <si>
-    <t xml:space="preserve">First down syndrome </t>
+    <t>Pleasant Valley Panthers</t>
   </si>
   <si>
     <t>Jimoke Jukes</t>
@@ -51,85 +54,73 @@
     <t>Wise Warlocks</t>
   </si>
   <si>
-    <t>Pleasant Valley Panthers</t>
-  </si>
-  <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>2-3</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.8%</t>
-  </si>
-  <si>
-    <t>99.6%</t>
-  </si>
-  <si>
-    <t>92.8%</t>
-  </si>
-  <si>
-    <t>82.5%</t>
-  </si>
-  <si>
-    <t>69.9%</t>
-  </si>
-  <si>
-    <t>41.9%</t>
-  </si>
-  <si>
-    <t>13.5%</t>
+    <t>99.7%</t>
+  </si>
+  <si>
+    <t>91.9%</t>
+  </si>
+  <si>
+    <t>77.7%</t>
+  </si>
+  <si>
+    <t>71.8%</t>
+  </si>
+  <si>
+    <t>34.4%</t>
+  </si>
+  <si>
+    <t>24.5%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-49900</t>
-  </si>
-  <si>
-    <t>-24900</t>
-  </si>
-  <si>
-    <t>-1289</t>
-  </si>
-  <si>
-    <t>-471</t>
-  </si>
-  <si>
-    <t>-232</t>
-  </si>
-  <si>
-    <t>+139</t>
-  </si>
-  <si>
-    <t>+641</t>
+    <t>-33233</t>
+  </si>
+  <si>
+    <t>-1135</t>
+  </si>
+  <si>
+    <t>-348</t>
+  </si>
+  <si>
+    <t>-255</t>
+  </si>
+  <si>
+    <t>+191</t>
+  </si>
+  <si>
+    <t>+308</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>82.3%</t>
-  </si>
-  <si>
-    <t>11.2%</t>
-  </si>
-  <si>
-    <t>6.0%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
+    <t>44.8%</t>
+  </si>
+  <si>
+    <t>35.8%</t>
+  </si>
+  <si>
+    <t>18.5%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
   </si>
   <si>
     <t>0.1%</t>
@@ -138,49 +129,49 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-465</t>
-  </si>
-  <si>
-    <t>+793</t>
-  </si>
-  <si>
-    <t>+1567</t>
-  </si>
-  <si>
-    <t>+24900</t>
+    <t>+123</t>
+  </si>
+  <si>
+    <t>+179</t>
+  </si>
+  <si>
+    <t>+441</t>
+  </si>
+  <si>
+    <t>+12400</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>65.1%</t>
-  </si>
-  <si>
-    <t>20.8%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>3.6%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>-187</t>
-  </si>
-  <si>
-    <t>+381</t>
-  </si>
-  <si>
-    <t>+999</t>
-  </si>
-  <si>
-    <t>+2678</t>
-  </si>
-  <si>
-    <t>+7043</t>
+    <t>44.3%</t>
+  </si>
+  <si>
+    <t>34.5%</t>
+  </si>
+  <si>
+    <t>11.3%</t>
+  </si>
+  <si>
+    <t>8.2%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>+126</t>
+  </si>
+  <si>
+    <t>+190</t>
+  </si>
+  <si>
+    <t>+785</t>
+  </si>
+  <si>
+    <t>+1120</t>
+  </si>
+  <si>
+    <t>+5782</t>
   </si>
 </sst>
 </file>
@@ -563,10 +554,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -574,13 +565,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -588,13 +579,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -602,13 +593,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -616,13 +607,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -630,13 +621,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -644,13 +635,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -658,13 +649,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -685,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -699,10 +690,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -710,13 +701,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -724,13 +715,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -738,13 +729,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -752,55 +743,55 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -821,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -832,13 +823,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -846,13 +837,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -860,13 +851,13 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -874,13 +865,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -888,55 +879,55 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/EBC League 2026 Betting Odds.xlsx
+++ b/data/odds/EBC League 2026 Betting Odds.xlsx
@@ -30,21 +30,21 @@
     <t>Team</t>
   </si>
   <si>
+    <t>OBJYN</t>
+  </si>
+  <si>
+    <t>Abyss Diamond Eyes</t>
+  </si>
+  <si>
     <t>Inter Miami CF</t>
   </si>
   <si>
-    <t>OBJYN</t>
-  </si>
-  <si>
-    <t>Abyss Diamond Eyes</t>
+    <t>P90 Asiimov</t>
   </si>
   <si>
     <t xml:space="preserve">First down syndrome </t>
   </si>
   <si>
-    <t>P90 Asiimov</t>
-  </si>
-  <si>
     <t>Pleasant Valley Panthers</t>
   </si>
   <si>
@@ -54,124 +54,124 @@
     <t>Wise Warlocks</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>2-3</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>3-3</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.7%</t>
-  </si>
-  <si>
-    <t>91.9%</t>
-  </si>
-  <si>
-    <t>77.7%</t>
-  </si>
-  <si>
-    <t>71.8%</t>
-  </si>
-  <si>
-    <t>34.4%</t>
-  </si>
-  <si>
-    <t>24.5%</t>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>93.5%</t>
+  </si>
+  <si>
+    <t>87.6%</t>
+  </si>
+  <si>
+    <t>78.5%</t>
+  </si>
+  <si>
+    <t>22.8%</t>
+  </si>
+  <si>
+    <t>17.7%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-33233</t>
-  </si>
-  <si>
-    <t>-1135</t>
-  </si>
-  <si>
-    <t>-348</t>
-  </si>
-  <si>
-    <t>-255</t>
-  </si>
-  <si>
-    <t>+191</t>
-  </si>
-  <si>
-    <t>+308</t>
+    <t>-1438</t>
+  </si>
+  <si>
+    <t>-706</t>
+  </si>
+  <si>
+    <t>-365</t>
+  </si>
+  <si>
+    <t>+339</t>
+  </si>
+  <si>
+    <t>+465</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>44.8%</t>
-  </si>
-  <si>
-    <t>35.8%</t>
-  </si>
-  <si>
-    <t>18.5%</t>
-  </si>
-  <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
+    <t>50.1%</t>
+  </si>
+  <si>
+    <t>26.5%</t>
+  </si>
+  <si>
+    <t>22.7%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>+123</t>
-  </si>
-  <si>
-    <t>+179</t>
-  </si>
-  <si>
-    <t>+441</t>
-  </si>
-  <si>
-    <t>+12400</t>
+    <t>-100</t>
+  </si>
+  <si>
+    <t>+277</t>
+  </si>
+  <si>
+    <t>+341</t>
+  </si>
+  <si>
+    <t>+19900</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>44.3%</t>
-  </si>
-  <si>
-    <t>34.5%</t>
-  </si>
-  <si>
-    <t>11.3%</t>
-  </si>
-  <si>
-    <t>8.2%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>+126</t>
-  </si>
-  <si>
-    <t>+190</t>
-  </si>
-  <si>
-    <t>+785</t>
-  </si>
-  <si>
-    <t>+1120</t>
-  </si>
-  <si>
-    <t>+5782</t>
+    <t>49.8%</t>
+  </si>
+  <si>
+    <t>39.4%</t>
+  </si>
+  <si>
+    <t>5.9%</t>
+  </si>
+  <si>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
+  </si>
+  <si>
+    <t>+101</t>
+  </si>
+  <si>
+    <t>+154</t>
+  </si>
+  <si>
+    <t>+1595</t>
+  </si>
+  <si>
+    <t>+2930</t>
+  </si>
+  <si>
+    <t>+6150</t>
   </si>
 </sst>
 </file>
@@ -565,7 +565,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
@@ -585,7 +585,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -593,13 +593,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -607,13 +607,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -627,7 +627,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -635,13 +635,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -649,13 +649,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -684,30 +684,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -718,10 +718,10 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -729,13 +729,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -743,13 +743,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -760,7 +760,7 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
         <v>41</v>
@@ -771,10 +771,10 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
         <v>41</v>
@@ -785,10 +785,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
         <v>41</v>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -823,7 +823,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>42</v>
@@ -837,7 +837,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>43</v>
@@ -865,7 +865,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>45</v>
@@ -879,7 +879,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
@@ -890,13 +890,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
         <v>41</v>
@@ -904,13 +904,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
         <v>41</v>
@@ -918,13 +918,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
         <v>41</v>

--- a/data/odds/EBC League 2026 Betting Odds.xlsx
+++ b/data/odds/EBC League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="57">
   <si>
     <t>Record</t>
   </si>
@@ -30,94 +30,103 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Inter Miami CF</t>
+  </si>
+  <si>
     <t>OBJYN</t>
   </si>
   <si>
     <t>Abyss Diamond Eyes</t>
   </si>
   <si>
-    <t>Inter Miami CF</t>
-  </si>
-  <si>
     <t>P90 Asiimov</t>
   </si>
   <si>
+    <t>Pleasant Valley Panthers</t>
+  </si>
+  <si>
     <t xml:space="preserve">First down syndrome </t>
   </si>
   <si>
-    <t>Pleasant Valley Panthers</t>
+    <t>Wise Warlocks</t>
   </si>
   <si>
     <t>Jimoke Jukes</t>
   </si>
   <si>
-    <t>Wise Warlocks</t>
-  </si>
-  <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>100.0%</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
   </si>
   <si>
     <t>99.9%</t>
   </si>
   <si>
-    <t>93.5%</t>
-  </si>
-  <si>
-    <t>87.6%</t>
-  </si>
-  <si>
-    <t>78.5%</t>
-  </si>
-  <si>
-    <t>22.8%</t>
-  </si>
-  <si>
-    <t>17.7%</t>
+    <t>99.7%</t>
+  </si>
+  <si>
+    <t>97.4%</t>
+  </si>
+  <si>
+    <t>86.2%</t>
+  </si>
+  <si>
+    <t>80.6%</t>
+  </si>
+  <si>
+    <t>20.2%</t>
+  </si>
+  <si>
+    <t>16.1%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-1438</t>
-  </si>
-  <si>
-    <t>-706</t>
-  </si>
-  <si>
-    <t>-365</t>
-  </si>
-  <si>
-    <t>+339</t>
-  </si>
-  <si>
-    <t>+465</t>
+    <t>-33233</t>
+  </si>
+  <si>
+    <t>-3746</t>
+  </si>
+  <si>
+    <t>-625</t>
+  </si>
+  <si>
+    <t>-415</t>
+  </si>
+  <si>
+    <t>+395</t>
+  </si>
+  <si>
+    <t>+521</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>50.1%</t>
-  </si>
-  <si>
-    <t>26.5%</t>
-  </si>
-  <si>
-    <t>22.7%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
+    <t>44.4%</t>
+  </si>
+  <si>
+    <t>33.6%</t>
+  </si>
+  <si>
+    <t>19.5%</t>
+  </si>
+  <si>
+    <t>2.0%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -126,16 +135,19 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-100</t>
-  </si>
-  <si>
-    <t>+277</t>
-  </si>
-  <si>
-    <t>+341</t>
-  </si>
-  <si>
-    <t>+19900</t>
+    <t>+125</t>
+  </si>
+  <si>
+    <t>+198</t>
+  </si>
+  <si>
+    <t>+413</t>
+  </si>
+  <si>
+    <t>+4900</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
   <si>
     <t>+49900</t>
@@ -144,34 +156,37 @@
     <t>+99900</t>
   </si>
   <si>
-    <t>49.8%</t>
-  </si>
-  <si>
-    <t>39.4%</t>
-  </si>
-  <si>
-    <t>5.9%</t>
-  </si>
-  <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
-  </si>
-  <si>
-    <t>+101</t>
-  </si>
-  <si>
-    <t>+154</t>
-  </si>
-  <si>
-    <t>+1595</t>
-  </si>
-  <si>
-    <t>+2930</t>
-  </si>
-  <si>
-    <t>+6150</t>
+    <t>48.3%</t>
+  </si>
+  <si>
+    <t>42.6%</t>
+  </si>
+  <si>
+    <t>5.7%</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>+107</t>
+  </si>
+  <si>
+    <t>+135</t>
+  </si>
+  <si>
+    <t>+1654</t>
+  </si>
+  <si>
+    <t>+3604</t>
+  </si>
+  <si>
+    <t>+16567</t>
   </si>
 </sst>
 </file>
@@ -554,10 +569,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -568,10 +583,10 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -579,13 +594,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -593,13 +608,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -610,10 +625,10 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -621,13 +636,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -635,13 +650,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -649,13 +664,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -676,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -684,30 +699,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -715,13 +730,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -729,69 +744,69 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -823,13 +838,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -837,13 +852,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -851,13 +866,13 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -868,10 +883,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -879,13 +894,13 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -893,13 +908,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -910,10 +925,10 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -924,10 +939,10 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/EBC League 2026 Betting Odds.xlsx
+++ b/data/odds/EBC League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="58">
   <si>
     <t>Record</t>
   </si>
@@ -69,61 +69,67 @@
     <t>2-5</t>
   </si>
   <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>99.7%</t>
-  </si>
-  <si>
-    <t>97.4%</t>
-  </si>
-  <si>
-    <t>86.2%</t>
-  </si>
-  <si>
-    <t>80.6%</t>
-  </si>
-  <si>
-    <t>20.2%</t>
-  </si>
-  <si>
-    <t>16.1%</t>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>99.4%</t>
+  </si>
+  <si>
+    <t>97.7%</t>
+  </si>
+  <si>
+    <t>87.0%</t>
+  </si>
+  <si>
+    <t>82.4%</t>
+  </si>
+  <si>
+    <t>18.8%</t>
+  </si>
+  <si>
+    <t>14.9%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-33233</t>
-  </si>
-  <si>
-    <t>-3746</t>
-  </si>
-  <si>
-    <t>-625</t>
-  </si>
-  <si>
-    <t>-415</t>
-  </si>
-  <si>
-    <t>+395</t>
-  </si>
-  <si>
-    <t>+521</t>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-16567</t>
+  </si>
+  <si>
+    <t>-4248</t>
+  </si>
+  <si>
+    <t>-669</t>
+  </si>
+  <si>
+    <t>-468</t>
+  </si>
+  <si>
+    <t>+432</t>
+  </si>
+  <si>
+    <t>+571</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>44.4%</t>
-  </si>
-  <si>
-    <t>33.6%</t>
-  </si>
-  <si>
-    <t>19.5%</t>
-  </si>
-  <si>
-    <t>2.0%</t>
+    <t>47.7%</t>
+  </si>
+  <si>
+    <t>32.7%</t>
+  </si>
+  <si>
+    <t>16.8%</t>
+  </si>
+  <si>
+    <t>2.3%</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -135,16 +141,16 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>+125</t>
-  </si>
-  <si>
-    <t>+198</t>
-  </si>
-  <si>
-    <t>+413</t>
-  </si>
-  <si>
-    <t>+4900</t>
+    <t>+110</t>
+  </si>
+  <si>
+    <t>+206</t>
+  </si>
+  <si>
+    <t>+495</t>
+  </si>
+  <si>
+    <t>+4248</t>
   </si>
   <si>
     <t>+33233</t>
@@ -156,37 +162,34 @@
     <t>+99900</t>
   </si>
   <si>
-    <t>48.3%</t>
-  </si>
-  <si>
-    <t>42.6%</t>
-  </si>
-  <si>
-    <t>5.7%</t>
-  </si>
-  <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
+    <t>48.4%</t>
+  </si>
+  <si>
+    <t>44.8%</t>
+  </si>
+  <si>
+    <t>3.5%</t>
+  </si>
+  <si>
+    <t>2.9%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
   </si>
   <si>
     <t>+107</t>
   </si>
   <si>
-    <t>+135</t>
-  </si>
-  <si>
-    <t>+1654</t>
-  </si>
-  <si>
-    <t>+3604</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>+123</t>
+  </si>
+  <si>
+    <t>+2757</t>
+  </si>
+  <si>
+    <t>+3348</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
 </sst>
 </file>
@@ -572,7 +575,7 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -583,10 +586,10 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -597,10 +600,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -611,10 +614,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -625,10 +628,10 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -639,10 +642,10 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -653,10 +656,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -667,10 +670,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -691,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -705,10 +708,10 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -719,10 +722,10 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -733,10 +736,10 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -747,38 +750,38 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -789,10 +792,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -803,10 +806,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -827,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -841,10 +844,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -855,10 +858,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -869,10 +872,10 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -883,10 +886,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -897,52 +900,52 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
